--- a/public/auto-awb-bulkUpload.xlsx
+++ b/public/auto-awb-bulkUpload.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11580"/>
+    <workbookView windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
   <si>
     <t>AccountCode</t>
   </si>
@@ -62,6 +62,15 @@
     <t>ActualWeight</t>
   </si>
   <si>
+    <t>HSNCode</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
     <t>ConsignorName</t>
   </si>
   <si>
@@ -119,19 +128,88 @@
     <t>ShipmentContent</t>
   </si>
   <si>
-    <t>HSNCode</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Rate</t>
-  </si>
-  <si>
     <t>InvoiceValue</t>
   </si>
   <si>
     <t>InvoiceCurrency</t>
+  </si>
+  <si>
+    <t>DL001</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>NJ</t>
+  </si>
+  <si>
+    <t>EX DEL US PR GR FEDEX</t>
+  </si>
+  <si>
+    <t>Dox</t>
+  </si>
+  <si>
+    <t>25,20</t>
+  </si>
+  <si>
+    <t>45,40</t>
+  </si>
+  <si>
+    <t>45,45</t>
+  </si>
+  <si>
+    <t>15.32,12.11</t>
+  </si>
+  <si>
+    <t>0031, 5647</t>
+  </si>
+  <si>
+    <t>20,10</t>
+  </si>
+  <si>
+    <t>500, 1500</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>bsp</t>
+  </si>
+  <si>
+    <t>cg</t>
+  </si>
+  <si>
+    <t>491559</t>
+  </si>
+  <si>
+    <t>6263792959</t>
+  </si>
+  <si>
+    <t>PAN</t>
+  </si>
+  <si>
+    <t>DJSKJJBAK35</t>
+  </si>
+  <si>
+    <t>0012</t>
+  </si>
+  <si>
+    <t>491551</t>
+  </si>
+  <si>
+    <t>suraj@test.com</t>
+  </si>
+  <si>
+    <t>Book</t>
+  </si>
+  <si>
+    <t>INR</t>
   </si>
 </sst>
 </file>
@@ -321,7 +399,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,6 +409,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -705,7 +789,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -729,16 +813,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -747,89 +831,89 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -837,20 +921,30 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1211,26 +1305,20 @@
     <col min="6" max="6" width="19.2857142857143" customWidth="1"/>
     <col min="8" max="10" width="21.8571428571429" customWidth="1"/>
     <col min="11" max="11" width="23.8571428571429" customWidth="1"/>
-    <col min="12" max="12" width="16.4285714285714" customWidth="1"/>
-    <col min="13" max="14" width="23.8571428571429" customWidth="1"/>
-    <col min="15" max="15" width="14.2857142857143" customWidth="1"/>
-    <col min="16" max="16" width="15.5714285714286" customWidth="1"/>
-    <col min="17" max="17" width="18.5714285714286" customWidth="1"/>
-    <col min="18" max="18" width="21.2857142857143" customWidth="1"/>
-    <col min="19" max="19" width="19.1428571428571" customWidth="1"/>
-    <col min="20" max="20" width="17.2857142857143" customWidth="1"/>
-    <col min="21" max="21" width="16.8571428571429" customWidth="1"/>
-    <col min="22" max="23" width="24.2857142857143" customWidth="1"/>
-    <col min="24" max="24" width="14.8571428571429" customWidth="1"/>
-    <col min="25" max="25" width="16.1428571428571" customWidth="1"/>
-    <col min="26" max="26" width="18.8571428571429" customWidth="1"/>
-    <col min="27" max="27" width="21.7142857142857" customWidth="1"/>
-    <col min="28" max="28" width="33.1428571428571" customWidth="1"/>
-    <col min="29" max="29" width="27" customWidth="1"/>
-    <col min="30" max="30" width="26.2857142857143" customWidth="1"/>
-    <col min="31" max="31" width="44" customWidth="1"/>
-    <col min="32" max="32" width="22.2857142857143" customWidth="1"/>
-    <col min="33" max="33" width="25.7142857142857" customWidth="1"/>
+    <col min="12" max="12" width="44" customWidth="1"/>
+    <col min="13" max="13" width="22.2857142857143" customWidth="1"/>
+    <col min="14" max="14" width="25.7142857142857" customWidth="1"/>
+    <col min="15" max="15" width="16.4285714285714" customWidth="1"/>
+    <col min="16" max="17" width="23.8571428571429" customWidth="1"/>
+    <col min="18" max="18" width="14.2857142857143" customWidth="1"/>
+    <col min="19" max="19" width="15.5714285714286" customWidth="1"/>
+    <col min="20" max="20" width="18.5714285714286" customWidth="1"/>
+    <col min="21" max="21" width="21.2857142857143" customWidth="1"/>
+    <col min="22" max="22" width="19.1428571428571" customWidth="1"/>
+    <col min="23" max="23" width="17.2857142857143" customWidth="1"/>
+    <col min="24" max="24" width="16.8571428571429" customWidth="1"/>
+    <col min="25" max="25" width="24.2857142857143" customWidth="1"/>
+    <col min="26" max="33" width="25.8571428571429" customWidth="1"/>
     <col min="34" max="34" width="23.5714285714286" customWidth="1"/>
     <col min="35" max="35" width="24.5714285714286" customWidth="1"/>
   </cols>
@@ -1257,25 +1345,25 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
@@ -1284,7 +1372,7 @@
       <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="2" t="s">
@@ -1302,7 +1390,7 @@
       <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="2" t="s">
@@ -1311,39 +1399,143 @@
       <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="9" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AE1" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="AF1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="8" t="s">
+      <c r="AG1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="7" t="s">
+      <c r="AH1" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AI1" s="12" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" spans="1:35">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T2" t="s">
+        <v>52</v>
+      </c>
+      <c r="U2" t="s">
+        <v>53</v>
+      </c>
+      <c r="V2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W2" t="s">
+        <v>55</v>
+      </c>
+      <c r="X2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH2">
+        <v>25000</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="2:2">
-      <c r="B8" s="3"/>
+      <c r="B8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/auto-awb-bulkUpload.xlsx
+++ b/public/auto-awb-bulkUpload.xlsx
@@ -222,7 +222,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,6 +242,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -783,133 +791,133 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -921,7 +929,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -935,10 +943,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
